--- a/clients/encore/testcases/item-search/item-search-product-groups.xlsx
+++ b/clients/encore/testcases/item-search/item-search-product-groups.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="106">
   <si>
     <t>TC ID</t>
   </si>
@@ -76,19 +76,22 @@
     <t>Medium</t>
   </si>
   <si>
-    <t>Pending Automation</t>
+    <t>Automated</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>The automation account has access to office 1101</t>
+  </si>
+  <si>
+    <t>1. On the Products page, select a result row and click Product Group in the toolbar</t>
+  </si>
+  <si>
+    <t>The Product Groups page opens</t>
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>The automation account has access to office 1101</t>
-  </si>
-  <si>
-    <t>1. On the Products page, select a result row and click Product Group in the toolbar</t>
-  </si>
-  <si>
-    <t>The Product Groups page opens</t>
   </si>
   <si>
     <t>2. Wait until no loading placeholders remain</t>
@@ -323,16 +326,16 @@
     <t>Item Search — Product Groups</t>
   </si>
   <si>
-    <t>Automated: 0 / Pending: 10</t>
-  </si>
-  <si>
-    <t>Not run in this delivery</t>
+    <t>Automated: 10 / Pending: 0</t>
+  </si>
+  <si>
+    <t>Pass:10 Fail:0 Skipped:0 Blocked:0</t>
   </si>
   <si>
     <t>Last Updated: 2026-08-31</t>
   </si>
   <si>
-    <t>f28c807cfb6eeb8b94ac190190f1358c8dc4f8c37d5142ffe46b461a0507db07</t>
+    <t>d96ccb59875274442c18342f06a9aa9c3097f6ed8a4e1cb1fd5e32267acbe42c</t>
   </si>
 </sst>
 </file>
@@ -731,7 +734,7 @@
     <col min="5" max="5" width="80" customWidth="1"/>
     <col min="6" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="28" customWidth="1"/>
-    <col min="9" max="9" width="26" customWidth="1"/>
+    <col min="9" max="9" width="36" customWidth="1"/>
     <col min="10" max="10" width="76" customWidth="1"/>
     <col min="11" max="12" width="80" customWidth="1"/>
     <col min="13" max="13" width="26" customWidth="1"/>
@@ -816,97 +819,97 @@
         <v>24</v>
       </c>
       <c r="M2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
         <v>15</v>
@@ -930,65 +933,65 @@
         <v>21</v>
       </c>
       <c r="J5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
         <v>15</v>
@@ -1012,65 +1015,65 @@
         <v>21</v>
       </c>
       <c r="J7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
         <v>15</v>
@@ -1079,7 +1082,7 @@
         <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -1094,106 +1097,106 @@
         <v>21</v>
       </c>
       <c r="J9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C12" t="s">
         <v>15</v>
@@ -1217,65 +1220,65 @@
         <v>21</v>
       </c>
       <c r="J12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D13" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E13" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F13" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G13" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H13" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I13" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J13" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M13" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s">
         <v>15</v>
@@ -1299,147 +1302,147 @@
         <v>21</v>
       </c>
       <c r="J14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M14" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D15" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E15" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F15" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G15" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H15" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I15" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J15" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M15" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D17" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E17" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F17" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G17" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H17" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I17" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J17" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M17" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C18" t="s">
         <v>15</v>
@@ -1463,65 +1466,65 @@
         <v>21</v>
       </c>
       <c r="J18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M18" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D19" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E19" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F19" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G19" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H19" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I19" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J19" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K19" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M19" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s">
         <v>15</v>
@@ -1545,65 +1548,65 @@
         <v>21</v>
       </c>
       <c r="J20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M20" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D21" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E21" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F21" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G21" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H21" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I21" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J21" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M21" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s">
         <v>15</v>
@@ -1627,65 +1630,65 @@
         <v>21</v>
       </c>
       <c r="J22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K22" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L22" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M22" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C23" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D23" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E23" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F23" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G23" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H23" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I23" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J23" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K23" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M23" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B24" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C24" t="s">
         <v>15</v>
@@ -1709,98 +1712,98 @@
         <v>21</v>
       </c>
       <c r="J24" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K24" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L24" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M24" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C25" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D25" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E25" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F25" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G25" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H25" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I25" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J25" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K25" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L25" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M25" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -1816,7 +1819,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/clients/encore/testcases/item-search/item-search-product-groups.xlsx
+++ b/clients/encore/testcases/item-search/item-search-product-groups.xlsx
@@ -335,7 +335,7 @@
     <t>Last Updated: 2026-08-31</t>
   </si>
   <si>
-    <t>d96ccb59875274442c18342f06a9aa9c3097f6ed8a4e1cb1fd5e32267acbe42c</t>
+    <t>49b6bbaa1b0534e99f83598cc30c0c62ecee0b835796d356c2fde35f8e610e29</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/item-search/item-search-product-groups.xlsx
+++ b/clients/encore/testcases/item-search/item-search-product-groups.xlsx
@@ -335,7 +335,7 @@
     <t>Last Updated: 2026-08-31</t>
   </si>
   <si>
-    <t>49b6bbaa1b0534e99f83598cc30c0c62ecee0b835796d356c2fde35f8e610e29</t>
+    <t>a5f7d6500d58722995e66601ec026824ea3e350a07badce9343a7a492d496f36</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/item-search/item-search-product-groups.xlsx
+++ b/clients/encore/testcases/item-search/item-search-product-groups.xlsx
@@ -335,7 +335,7 @@
     <t>Last Updated: 2026-08-31</t>
   </si>
   <si>
-    <t>a5f7d6500d58722995e66601ec026824ea3e350a07badce9343a7a492d496f36</t>
+    <t>636a977849267dc2016113abf29c1c780ee08ec327c6f8ab32a1e036b3a6cf92</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/item-search/item-search-product-groups.xlsx
+++ b/clients/encore/testcases/item-search/item-search-product-groups.xlsx
@@ -335,7 +335,7 @@
     <t>Last Updated: 2026-08-31</t>
   </si>
   <si>
-    <t>636a977849267dc2016113abf29c1c780ee08ec327c6f8ab32a1e036b3a6cf92</t>
+    <t>9b801757218047b86420f352cec3e581306b4bdd9151437dfc89dac28f323abc</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/item-search/item-search-product-groups.xlsx
+++ b/clients/encore/testcases/item-search/item-search-product-groups.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="119">
   <si>
     <t>TC ID</t>
   </si>
@@ -320,22 +320,61 @@
     <t>Each row carries a service type (e.g. `Equipment Rental`)</t>
   </si>
   <si>
+    <t>TC-ISR-PGR-011</t>
+  </si>
+  <si>
+    <t>A completed Add page saves a new product group and it is found again</t>
+  </si>
+  <si>
+    <t>The Product Groups page is open for office 1101</t>
+  </si>
+  <si>
+    <t>1. Click Add, then fill Name and Description with a per-run unique value (e.g. a ZZ-E2E-&lt;timestamp&gt; name)</t>
+  </si>
+  <si>
+    <t>Both required fields hold the typed values, read back from the boxes</t>
+  </si>
+  <si>
+    <t>2. Choose a Service Type</t>
+  </si>
+  <si>
+    <t>The Service Type selector shows the chosen value</t>
+  </si>
+  <si>
+    <t>3. In the sub-class picker, double-click one item in the left list</t>
+  </si>
+  <si>
+    <t>The item moves to the Sub Classes area on the right, and — with Name, Description, Service Type and one sub-class all set — Save enables</t>
+  </si>
+  <si>
+    <t>4. Click Save</t>
+  </si>
+  <si>
+    <t>A "Product Group created successfully" toast appears and the page redirects to the groups list; `POST /navigator/api/location/add-update-product-group` returns 200</t>
+  </si>
+  <si>
+    <t>5. Search the groups list for the new group's exact Name</t>
+  </si>
+  <si>
+    <t>Exactly one row returns — the group just created, showing its Description and Service Type</t>
+  </si>
+  <si>
     <t>SUMMARY</t>
   </si>
   <si>
     <t>Item Search — Product Groups</t>
   </si>
   <si>
-    <t>Automated: 10 / Pending: 0</t>
-  </si>
-  <si>
-    <t>Pass:10 Fail:0 Skipped:0 Blocked:0</t>
-  </si>
-  <si>
-    <t>Last Updated: 2026-08-31</t>
-  </si>
-  <si>
-    <t>9b801757218047b86420f352cec3e581306b4bdd9151437dfc89dac28f323abc</t>
+    <t>Automated: 11 / Pending: 0</t>
+  </si>
+  <si>
+    <t>Pass:11 Fail:0 Skipped:0 Blocked:0</t>
+  </si>
+  <si>
+    <t>Last Updated: 2026-09-02</t>
+  </si>
+  <si>
+    <t>5d305d3fb952234794b61cbeff61034b41936a8d4e528edede656f33d539f3b0</t>
   </si>
 </sst>
 </file>
@@ -724,11 +763,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="57" customWidth="1"/>
+    <col min="2" max="2" width="70" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="80" customWidth="1"/>
@@ -1765,45 +1804,250 @@
         <v>25</v>
       </c>
     </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>100</v>
+      </c>
+      <c r="B26" t="s">
+        <v>101</v>
+      </c>
+      <c r="C26" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" t="s">
+        <v>17</v>
+      </c>
+      <c r="F26" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" t="s">
+        <v>19</v>
+      </c>
+      <c r="H26" t="s">
+        <v>20</v>
+      </c>
+      <c r="I26" t="s">
+        <v>21</v>
+      </c>
+      <c r="J26" t="s">
+        <v>102</v>
+      </c>
+      <c r="K26" t="s">
+        <v>103</v>
+      </c>
+      <c r="L26" t="s">
+        <v>104</v>
+      </c>
+      <c r="M26" t="s">
+        <v>25</v>
+      </c>
+    </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M27" s="2" t="s">
-        <v>104</v>
+      <c r="A27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D27" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" t="s">
+        <v>25</v>
+      </c>
+      <c r="G27" t="s">
+        <v>25</v>
+      </c>
+      <c r="H27" t="s">
+        <v>25</v>
+      </c>
+      <c r="I27" t="s">
+        <v>25</v>
+      </c>
+      <c r="J27" t="s">
+        <v>25</v>
+      </c>
+      <c r="K27" t="s">
+        <v>105</v>
+      </c>
+      <c r="L27" t="s">
+        <v>106</v>
+      </c>
+      <c r="M27" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D28" t="s">
+        <v>25</v>
+      </c>
+      <c r="E28" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" t="s">
+        <v>25</v>
+      </c>
+      <c r="G28" t="s">
+        <v>25</v>
+      </c>
+      <c r="H28" t="s">
+        <v>25</v>
+      </c>
+      <c r="I28" t="s">
+        <v>25</v>
+      </c>
+      <c r="J28" t="s">
+        <v>25</v>
+      </c>
+      <c r="K28" t="s">
+        <v>107</v>
+      </c>
+      <c r="L28" t="s">
+        <v>108</v>
+      </c>
+      <c r="M28" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" t="s">
+        <v>25</v>
+      </c>
+      <c r="D29" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" t="s">
+        <v>25</v>
+      </c>
+      <c r="F29" t="s">
+        <v>25</v>
+      </c>
+      <c r="G29" t="s">
+        <v>25</v>
+      </c>
+      <c r="H29" t="s">
+        <v>25</v>
+      </c>
+      <c r="I29" t="s">
+        <v>25</v>
+      </c>
+      <c r="J29" t="s">
+        <v>25</v>
+      </c>
+      <c r="K29" t="s">
+        <v>109</v>
+      </c>
+      <c r="L29" t="s">
+        <v>110</v>
+      </c>
+      <c r="M29" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" t="s">
+        <v>25</v>
+      </c>
+      <c r="C30" t="s">
+        <v>25</v>
+      </c>
+      <c r="D30" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" t="s">
+        <v>25</v>
+      </c>
+      <c r="G30" t="s">
+        <v>25</v>
+      </c>
+      <c r="H30" t="s">
+        <v>25</v>
+      </c>
+      <c r="I30" t="s">
+        <v>25</v>
+      </c>
+      <c r="J30" t="s">
+        <v>25</v>
+      </c>
+      <c r="K30" t="s">
+        <v>111</v>
+      </c>
+      <c r="L30" t="s">
+        <v>112</v>
+      </c>
+      <c r="M30" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -1819,7 +2063,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/clients/encore/testcases/item-search/item-search-product-groups.xlsx
+++ b/clients/encore/testcases/item-search/item-search-product-groups.xlsx
@@ -5,14 +5,13 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="item_search_product_groups" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="__fp__" state="hidden" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="118">
   <si>
     <t>TC ID</t>
   </si>
@@ -372,9 +371,6 @@
   </si>
   <si>
     <t>Last Updated: 2026-09-02</t>
-  </si>
-  <si>
-    <t>5d305d3fb952234794b61cbeff61034b41936a8d4e528edede656f33d539f3b0</t>
   </si>
 </sst>
 </file>
@@ -2054,20 +2050,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
 </file>